--- a/output_files/LIBRUS Synergia.xlsx
+++ b/output_files/LIBRUS Synergia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,35 +446,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Okres 1: (I)</t>
+          <t>Okres 1: I</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Okres 1:I</t>
+          <t>Okres 2: Oceny Bieżące</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Okres 2: Oceny Bieżące</t>
+          <t>Okres 2: Śr.II</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Okres 2: Śr.II</t>
+          <t>Okres 2: II</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Okres 2: II</t>
+          <t>Koniec roku: Sr.R</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Koniec roku: Sr.R</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Koniec roku: R</t>
         </is>
@@ -488,118 +483,106 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3 np np</t>
+          <t>3 +</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4 3</t>
+          <t>+</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Edukacja zdrowotna</t>
+          <t>Biznes i zarządzanie</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Brak ocen</t>
+          <t>3 4 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Brak ocen</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Geografia</t>
+          <t>Chemia</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>+ + 3+ 5- 5+ 4-</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>[ 1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2 ][ 1 2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>- ]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Edukacja Obywatelska</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5 4 1</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Godzina wychowawcza</t>
+          <t>Edukacja Zdrowotna</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -609,474 +592,375 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Brak ocen</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Historia</t>
+          <t>Fizyka</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4+ 4+ 5</t>
+          <t>1 [ 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0 0</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>np 2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>] bz 5+</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Informatyka</t>
+          <t>Geografia</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>+ 5 5 5</t>
+          <t>[ 1 5 [ n</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5 5 5 5</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>1 4 ][ 1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3 ][ nb 2 ]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Brak ocen</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Język angielski</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>+ + 5 + + 5 + + + + 3 5</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>np 5 + 0 3</t>
+          <t>b 3+ ]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>+ 6 + +</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Język polski</t>
+          <t>Godzina wychowawcza</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4 5 5 +</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>+ 5 np 2+ 3 4+ 4 4+</t>
-        </is>
-      </c>
+          <t>Brak ocen</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6 - 0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Historia</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4+ 4 5 0</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>2 1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2+</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Matematyka</t>
+          <t>Informatyka</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>+ 6 3 5 5 3- - [ 1</t>
+          <t>6 5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4 [ 3 6 ] 1 1 3 1 ] 1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3+</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Język angielski</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Muzyka</t>
+          <t>Język hiszpański</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6 5+ + 5</t>
+          <t>T +</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5+ 5-</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>+ +</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>T T T</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Plastyka</t>
+          <t>Język polski</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5 5 5</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>4 4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4 3+ np 4+ 3- 1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Brak ocen</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Religia</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Brak ocen</t>
+          <t>3+</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Brak ocen</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Technika</t>
+          <t>Kultura Hiszpanii</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5- + bz</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Brak ocen</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Wychowanie fizyczne</t>
+          <t>Literatura hiszpańska</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>np np 5 5 4+ 5</t>
+          <t>T T T T T</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Brak ocen</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Zachowanie</t>
+          <t>Matematyka</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+          <t>2+</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>4 [ 2 -</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>] 1 1</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>bardzo dobre</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Religia</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kateg</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>oria Komentarz</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Oceny</t>
-        </is>
-      </c>
+          <t>Brak ocen</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Data wystawienia</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Wychowanie fizyczne</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Okres 1</t>
+          <t>+ np np + + + np +</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -1084,161 +968,156 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Czynny ud akcjach sz</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>ział w K kolnych.</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Zachowanie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>bardzo dobre</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Punkty startowe</t>
+          <t>Kategoria</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Komentarz</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Oceny</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Data wystawienia</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Suma</t>
+          <t>Okres 1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Brak ocen</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Ocena śródroczna przewidywana wystawiona przez nauczyciela: bardzo dobre</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ocena opisowa śródroczna</t>
+          <t>Punkty startowe</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Okres 2</t>
+          <t>Suma</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Brak ocen</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Ocena śródroczna przewidywana wystawiona przez nauczyciela:</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Punkty startowe</t>
+          <t>Ocena opisowa śródroczna</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -1250,7 +1129,6 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -1262,7 +1140,6 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -1274,7 +1151,6 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
